--- a/02_Zero_Shot/outputs/Embedding/ALBERT-base-v2/RESULT_pan_albert-base-v2_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/ALBERT-base-v2/RESULT_pan_albert-base-v2_zeroshot.xlsx
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.196042670999759</v>
+        <v>15.87571614699846</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001579886813668892</v>
+        <v>0.01142137852302047</v>
       </c>
     </row>
   </sheetData>
